--- a/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/RVTools_tabvCPU.xlsx
+++ b/PAMaap/app/archives/XLXS_IMPORT/ALIMENTADORES/RVTools_tabvCPU.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\carlos.bedoya\Documents\Documentacion\Equipo Infra\Capacidad\RvTools\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Desktop\autompython\PAMaap\app\archives\XLXS_IMPORT\ALIMENTADORES\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A300917B-6F29-4A70-B748-289BDCF586FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="vCPU" sheetId="2" r:id="rId1"/>
@@ -958,7 +957,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -1024,7 +1023,25 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="8">
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <color theme="0"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+      <fill>
+        <gradientFill degree="90">
+          <stop position="0">
+            <color rgb="FFC00000"/>
+          </stop>
+          <stop position="1">
+            <color rgb="FFFF0000"/>
+          </stop>
+        </gradientFill>
+      </fill>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1034,6 +1051,124 @@
           <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="Verdana"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="Verdana"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="Verdana"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="Verdana"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="Verdana"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FFFFFFFF"/>
+        <name val="Verdana"/>
+        <scheme val="none"/>
+      </font>
+      <numFmt numFmtId="3" formatCode="#,##0"/>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1046,6 +1181,19 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Tabla1" displayName="Tabla1" ref="A1:D307" totalsRowShown="0" headerRowDxfId="7" dataDxfId="6">
+  <autoFilter ref="A1:D307"/>
+  <tableColumns count="4">
+    <tableColumn id="1" name="VM" dataDxfId="5"/>
+    <tableColumn id="2" name="CPUs" dataDxfId="4"/>
+    <tableColumn id="3" name="Sockets" dataDxfId="3"/>
+    <tableColumn id="4" name="Cores p/s" dataDxfId="2"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium22" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1332,19 +1480,19 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D307"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.109375" defaultRowHeight="11.4" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="11.25" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="21.33203125" style="2" customWidth="1"/>
-    <col min="2" max="2" width="9.44140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="21.28515625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="9.42578125" style="3" customWidth="1"/>
     <col min="3" max="3" width="12" style="3" customWidth="1"/>
     <col min="4" max="4" width="14" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9.109375" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9.109375" style="1"/>
+    <col min="5" max="5" width="9.140625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
@@ -1358,7 +1506,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>4</v>
       </c>
@@ -1372,7 +1520,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
@@ -1386,7 +1534,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4" s="2" t="s">
         <v>6</v>
       </c>
@@ -1400,7 +1548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -1414,7 +1562,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1428,7 +1576,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7" s="2" t="s">
         <v>9</v>
       </c>
@@ -1442,7 +1590,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8" s="2" t="s">
         <v>10</v>
       </c>
@@ -1456,7 +1604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9" s="2" t="s">
         <v>11</v>
       </c>
@@ -1470,7 +1618,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10" s="2" t="s">
         <v>12</v>
       </c>
@@ -1484,7 +1632,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11" s="2" t="s">
         <v>13</v>
       </c>
@@ -1498,7 +1646,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A12" s="2" t="s">
         <v>14</v>
       </c>
@@ -1512,7 +1660,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13" s="2" t="s">
         <v>15</v>
       </c>
@@ -1526,7 +1674,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A14" s="2" t="s">
         <v>16</v>
       </c>
@@ -1540,7 +1688,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15" s="2" t="s">
         <v>17</v>
       </c>
@@ -1554,7 +1702,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16" s="2" t="s">
         <v>18</v>
       </c>
@@ -1568,7 +1716,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17" s="2" t="s">
         <v>19</v>
       </c>
@@ -1582,7 +1730,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18" s="2" t="s">
         <v>20</v>
       </c>
@@ -1596,7 +1744,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19" s="2" t="s">
         <v>21</v>
       </c>
@@ -1610,7 +1758,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20" s="2" t="s">
         <v>22</v>
       </c>
@@ -1624,7 +1772,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21" s="2" t="s">
         <v>23</v>
       </c>
@@ -1638,7 +1786,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22" s="2" t="s">
         <v>24</v>
       </c>
@@ -1652,7 +1800,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23" s="2" t="s">
         <v>25</v>
       </c>
@@ -1666,7 +1814,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24" s="2" t="s">
         <v>26</v>
       </c>
@@ -1680,7 +1828,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -1694,7 +1842,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26" s="2" t="s">
         <v>28</v>
       </c>
@@ -1708,7 +1856,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27" s="2" t="s">
         <v>29</v>
       </c>
@@ -1722,7 +1870,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A28" s="2" t="s">
         <v>30</v>
       </c>
@@ -1736,7 +1884,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A29" s="2" t="s">
         <v>31</v>
       </c>
@@ -1750,7 +1898,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -1764,7 +1912,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A31" s="2" t="s">
         <v>33</v>
       </c>
@@ -1778,7 +1926,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A32" s="2" t="s">
         <v>34</v>
       </c>
@@ -1792,7 +1940,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A33" s="2" t="s">
         <v>35</v>
       </c>
@@ -1806,7 +1954,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34" s="2" t="s">
         <v>36</v>
       </c>
@@ -1820,7 +1968,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A35" s="2" t="s">
         <v>37</v>
       </c>
@@ -1834,7 +1982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A36" s="2" t="s">
         <v>38</v>
       </c>
@@ -1848,7 +1996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A37" s="2" t="s">
         <v>39</v>
       </c>
@@ -1862,7 +2010,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A38" s="2" t="s">
         <v>40</v>
       </c>
@@ -1876,7 +2024,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A39" s="2" t="s">
         <v>41</v>
       </c>
@@ -1890,7 +2038,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A40" s="2" t="s">
         <v>42</v>
       </c>
@@ -1904,7 +2052,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A41" s="2" t="s">
         <v>43</v>
       </c>
@@ -1918,7 +2066,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42" s="2" t="s">
         <v>44</v>
       </c>
@@ -1932,7 +2080,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A43" s="2" t="s">
         <v>45</v>
       </c>
@@ -1946,7 +2094,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A44" s="2" t="s">
         <v>46</v>
       </c>
@@ -1960,7 +2108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A45" s="2" t="s">
         <v>47</v>
       </c>
@@ -1974,7 +2122,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A46" s="2" t="s">
         <v>48</v>
       </c>
@@ -1988,7 +2136,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A47" s="2" t="s">
         <v>49</v>
       </c>
@@ -2002,7 +2150,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A48" s="2" t="s">
         <v>50</v>
       </c>
@@ -2016,7 +2164,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A49" s="2" t="s">
         <v>51</v>
       </c>
@@ -2030,7 +2178,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A50" s="2" t="s">
         <v>52</v>
       </c>
@@ -2044,7 +2192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A51" s="2" t="s">
         <v>53</v>
       </c>
@@ -2058,7 +2206,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A52" s="2" t="s">
         <v>54</v>
       </c>
@@ -2072,7 +2220,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A53" s="2" t="s">
         <v>55</v>
       </c>
@@ -2086,7 +2234,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A54" s="2" t="s">
         <v>56</v>
       </c>
@@ -2100,7 +2248,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A55" s="2" t="s">
         <v>57</v>
       </c>
@@ -2114,7 +2262,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A56" s="2" t="s">
         <v>58</v>
       </c>
@@ -2128,7 +2276,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A57" s="2" t="s">
         <v>59</v>
       </c>
@@ -2142,7 +2290,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A58" s="2" t="s">
         <v>60</v>
       </c>
@@ -2156,7 +2304,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A59" s="2" t="s">
         <v>61</v>
       </c>
@@ -2170,7 +2318,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A60" s="2" t="s">
         <v>62</v>
       </c>
@@ -2184,7 +2332,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A61" s="2" t="s">
         <v>63</v>
       </c>
@@ -2198,7 +2346,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A62" s="2" t="s">
         <v>64</v>
       </c>
@@ -2212,7 +2360,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A63" s="2" t="s">
         <v>65</v>
       </c>
@@ -2226,7 +2374,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A64" s="2" t="s">
         <v>66</v>
       </c>
@@ -2240,7 +2388,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A65" s="2" t="s">
         <v>67</v>
       </c>
@@ -2254,7 +2402,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="66" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A66" s="2" t="s">
         <v>68</v>
       </c>
@@ -2268,7 +2416,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="67" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A67" s="2" t="s">
         <v>69</v>
       </c>
@@ -2282,7 +2430,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="68" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A68" s="2" t="s">
         <v>70</v>
       </c>
@@ -2296,7 +2444,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="69" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A69" s="2" t="s">
         <v>71</v>
       </c>
@@ -2310,7 +2458,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="70" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A70" s="2" t="s">
         <v>72</v>
       </c>
@@ -2324,7 +2472,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="71" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A71" s="2" t="s">
         <v>73</v>
       </c>
@@ -2338,7 +2486,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="72" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A72" s="2" t="s">
         <v>74</v>
       </c>
@@ -2352,7 +2500,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="73" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A73" s="2" t="s">
         <v>75</v>
       </c>
@@ -2366,7 +2514,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="74" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A74" s="2" t="s">
         <v>76</v>
       </c>
@@ -2380,7 +2528,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="75" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A75" s="2" t="s">
         <v>77</v>
       </c>
@@ -2394,7 +2542,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="76" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A76" s="2" t="s">
         <v>78</v>
       </c>
@@ -2408,7 +2556,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="77" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A77" s="2" t="s">
         <v>79</v>
       </c>
@@ -2422,7 +2570,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="78" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A78" s="2" t="s">
         <v>80</v>
       </c>
@@ -2436,7 +2584,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="79" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A79" s="2" t="s">
         <v>81</v>
       </c>
@@ -2450,7 +2598,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="80" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A80" s="2" t="s">
         <v>82</v>
       </c>
@@ -2464,7 +2612,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A81" s="2" t="s">
         <v>83</v>
       </c>
@@ -2478,7 +2626,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A82" s="2" t="s">
         <v>84</v>
       </c>
@@ -2492,7 +2640,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A83" s="2" t="s">
         <v>85</v>
       </c>
@@ -2506,7 +2654,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A84" s="2" t="s">
         <v>86</v>
       </c>
@@ -2520,7 +2668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A85" s="2" t="s">
         <v>87</v>
       </c>
@@ -2534,7 +2682,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A86" s="2" t="s">
         <v>88</v>
       </c>
@@ -2548,7 +2696,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A87" s="2" t="s">
         <v>89</v>
       </c>
@@ -2562,7 +2710,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A88" s="2" t="s">
         <v>90</v>
       </c>
@@ -2576,7 +2724,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A89" s="2" t="s">
         <v>91</v>
       </c>
@@ -2590,7 +2738,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A90" s="2" t="s">
         <v>92</v>
       </c>
@@ -2604,7 +2752,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A91" s="2" t="s">
         <v>93</v>
       </c>
@@ -2618,7 +2766,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A92" s="2" t="s">
         <v>94</v>
       </c>
@@ -2632,7 +2780,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A93" s="2" t="s">
         <v>95</v>
       </c>
@@ -2646,7 +2794,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A94" s="2" t="s">
         <v>96</v>
       </c>
@@ -2660,7 +2808,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A95" s="2" t="s">
         <v>97</v>
       </c>
@@ -2674,7 +2822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="96" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A96" s="2" t="s">
         <v>98</v>
       </c>
@@ -2688,7 +2836,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="97" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A97" s="2" t="s">
         <v>99</v>
       </c>
@@ -2702,7 +2850,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="98" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A98" s="2" t="s">
         <v>100</v>
       </c>
@@ -2716,7 +2864,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="99" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A99" s="2" t="s">
         <v>101</v>
       </c>
@@ -2730,7 +2878,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="100" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A100" s="2" t="s">
         <v>102</v>
       </c>
@@ -2744,7 +2892,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="101" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A101" s="2" t="s">
         <v>103</v>
       </c>
@@ -2758,7 +2906,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="102" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A102" s="2" t="s">
         <v>104</v>
       </c>
@@ -2772,7 +2920,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="103" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A103" s="2" t="s">
         <v>105</v>
       </c>
@@ -2786,7 +2934,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="104" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A104" s="2" t="s">
         <v>106</v>
       </c>
@@ -2800,7 +2948,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="105" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A105" s="2" t="s">
         <v>107</v>
       </c>
@@ -2814,7 +2962,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="106" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A106" s="2" t="s">
         <v>108</v>
       </c>
@@ -2828,7 +2976,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="107" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A107" s="2" t="s">
         <v>109</v>
       </c>
@@ -2842,7 +2990,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="108" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A108" s="2" t="s">
         <v>110</v>
       </c>
@@ -2856,7 +3004,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="109" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A109" s="2" t="s">
         <v>111</v>
       </c>
@@ -2870,7 +3018,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="110" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A110" s="2" t="s">
         <v>112</v>
       </c>
@@ -2884,7 +3032,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="111" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A111" s="2" t="s">
         <v>113</v>
       </c>
@@ -2898,7 +3046,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="112" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A112" s="2" t="s">
         <v>114</v>
       </c>
@@ -2912,7 +3060,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A113" s="2" t="s">
         <v>115</v>
       </c>
@@ -2926,7 +3074,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="114" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A114" s="2" t="s">
         <v>116</v>
       </c>
@@ -2940,7 +3088,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="115" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A115" s="2" t="s">
         <v>117</v>
       </c>
@@ -2954,7 +3102,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="116" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A116" s="2" t="s">
         <v>118</v>
       </c>
@@ -2968,7 +3116,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="117" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A117" s="2" t="s">
         <v>119</v>
       </c>
@@ -2982,7 +3130,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="118" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A118" s="2" t="s">
         <v>120</v>
       </c>
@@ -2996,7 +3144,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="119" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A119" s="2" t="s">
         <v>121</v>
       </c>
@@ -3010,7 +3158,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="120" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A120" s="2" t="s">
         <v>122</v>
       </c>
@@ -3024,7 +3172,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="121" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A121" s="2" t="s">
         <v>123</v>
       </c>
@@ -3038,7 +3186,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="122" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A122" s="2" t="s">
         <v>124</v>
       </c>
@@ -3052,7 +3200,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="123" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A123" s="2" t="s">
         <v>125</v>
       </c>
@@ -3066,7 +3214,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="124" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A124" s="2" t="s">
         <v>126</v>
       </c>
@@ -3080,7 +3228,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="125" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A125" s="2" t="s">
         <v>127</v>
       </c>
@@ -3094,7 +3242,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="126" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A126" s="2" t="s">
         <v>128</v>
       </c>
@@ -3108,7 +3256,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="127" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A127" s="2" t="s">
         <v>129</v>
       </c>
@@ -3122,7 +3270,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="128" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A128" s="2" t="s">
         <v>130</v>
       </c>
@@ -3136,7 +3284,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="129" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A129" s="2" t="s">
         <v>131</v>
       </c>
@@ -3150,7 +3298,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="130" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A130" s="2" t="s">
         <v>132</v>
       </c>
@@ -3164,7 +3312,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="131" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A131" s="2" t="s">
         <v>133</v>
       </c>
@@ -3178,7 +3326,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="132" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A132" s="2" t="s">
         <v>134</v>
       </c>
@@ -3192,7 +3340,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="133" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A133" s="2" t="s">
         <v>135</v>
       </c>
@@ -3206,7 +3354,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="134" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A134" s="2" t="s">
         <v>136</v>
       </c>
@@ -3220,7 +3368,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="135" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A135" s="2" t="s">
         <v>137</v>
       </c>
@@ -3234,7 +3382,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="136" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A136" s="2" t="s">
         <v>138</v>
       </c>
@@ -3248,7 +3396,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="137" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A137" s="2" t="s">
         <v>139</v>
       </c>
@@ -3262,7 +3410,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="138" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A138" s="2" t="s">
         <v>140</v>
       </c>
@@ -3276,7 +3424,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="139" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A139" s="2" t="s">
         <v>141</v>
       </c>
@@ -3290,7 +3438,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="140" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A140" s="2" t="s">
         <v>142</v>
       </c>
@@ -3304,7 +3452,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="141" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A141" s="2" t="s">
         <v>143</v>
       </c>
@@ -3318,7 +3466,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="142" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A142" s="2" t="s">
         <v>144</v>
       </c>
@@ -3332,7 +3480,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="143" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A143" s="2" t="s">
         <v>145</v>
       </c>
@@ -3346,7 +3494,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="144" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A144" s="2" t="s">
         <v>146</v>
       </c>
@@ -3360,7 +3508,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="145" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A145" s="2" t="s">
         <v>147</v>
       </c>
@@ -3374,7 +3522,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="146" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A146" s="2" t="s">
         <v>148</v>
       </c>
@@ -3388,7 +3536,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="147" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A147" s="2" t="s">
         <v>149</v>
       </c>
@@ -3402,7 +3550,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="148" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A148" s="2" t="s">
         <v>150</v>
       </c>
@@ -3416,7 +3564,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="149" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A149" s="2" t="s">
         <v>151</v>
       </c>
@@ -3430,7 +3578,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="150" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A150" s="2" t="s">
         <v>152</v>
       </c>
@@ -3444,7 +3592,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="151" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A151" s="2" t="s">
         <v>153</v>
       </c>
@@ -3458,7 +3606,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="152" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A152" s="2" t="s">
         <v>154</v>
       </c>
@@ -3472,7 +3620,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="153" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A153" s="2" t="s">
         <v>155</v>
       </c>
@@ -3486,7 +3634,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="154" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="154" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A154" s="2" t="s">
         <v>156</v>
       </c>
@@ -3500,7 +3648,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="155" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="155" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A155" s="2" t="s">
         <v>157</v>
       </c>
@@ -3514,7 +3662,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="156" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="156" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A156" s="2" t="s">
         <v>158</v>
       </c>
@@ -3528,7 +3676,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="157" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="157" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A157" s="2" t="s">
         <v>159</v>
       </c>
@@ -3542,7 +3690,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="158" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="158" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A158" s="2" t="s">
         <v>160</v>
       </c>
@@ -3556,7 +3704,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="159" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="159" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A159" s="2" t="s">
         <v>161</v>
       </c>
@@ -3570,7 +3718,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="160" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="160" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A160" s="2" t="s">
         <v>162</v>
       </c>
@@ -3584,7 +3732,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="161" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A161" s="2" t="s">
         <v>163</v>
       </c>
@@ -3598,7 +3746,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="162" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="162" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A162" s="2" t="s">
         <v>164</v>
       </c>
@@ -3612,7 +3760,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="163" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="163" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A163" s="2" t="s">
         <v>165</v>
       </c>
@@ -3626,7 +3774,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="164" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="164" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A164" s="2" t="s">
         <v>166</v>
       </c>
@@ -3640,7 +3788,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="165" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="165" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A165" s="2" t="s">
         <v>167</v>
       </c>
@@ -3654,7 +3802,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="166" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="166" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A166" s="2" t="s">
         <v>168</v>
       </c>
@@ -3668,7 +3816,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="167" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="167" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A167" s="2" t="s">
         <v>169</v>
       </c>
@@ -3682,7 +3830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="168" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A168" s="2" t="s">
         <v>170</v>
       </c>
@@ -3696,7 +3844,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="169" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="169" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A169" s="2" t="s">
         <v>171</v>
       </c>
@@ -3710,7 +3858,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="170" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="170" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A170" s="2" t="s">
         <v>172</v>
       </c>
@@ -3724,7 +3872,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="171" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="171" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A171" s="2" t="s">
         <v>173</v>
       </c>
@@ -3738,7 +3886,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="172" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="172" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A172" s="2" t="s">
         <v>174</v>
       </c>
@@ -3752,7 +3900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="173" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="173" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A173" s="2" t="s">
         <v>175</v>
       </c>
@@ -3766,7 +3914,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="174" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="174" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A174" s="2" t="s">
         <v>176</v>
       </c>
@@ -3780,7 +3928,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="175" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="175" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A175" s="2" t="s">
         <v>177</v>
       </c>
@@ -3794,7 +3942,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="176" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="176" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A176" s="2" t="s">
         <v>178</v>
       </c>
@@ -3808,7 +3956,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="177" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="177" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A177" s="2" t="s">
         <v>179</v>
       </c>
@@ -3822,7 +3970,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="178" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="178" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A178" s="2" t="s">
         <v>180</v>
       </c>
@@ -3836,7 +3984,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="179" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="179" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A179" s="2" t="s">
         <v>181</v>
       </c>
@@ -3850,7 +3998,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="180" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="180" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A180" s="2" t="s">
         <v>182</v>
       </c>
@@ -3864,7 +4012,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="181" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="181" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A181" s="2" t="s">
         <v>183</v>
       </c>
@@ -3878,7 +4026,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="182" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="182" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A182" s="2" t="s">
         <v>184</v>
       </c>
@@ -3892,7 +4040,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="183" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="183" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A183" s="2" t="s">
         <v>185</v>
       </c>
@@ -3906,7 +4054,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="184" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="184" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A184" s="2" t="s">
         <v>186</v>
       </c>
@@ -3920,7 +4068,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="185" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="185" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A185" s="2" t="s">
         <v>187</v>
       </c>
@@ -3934,7 +4082,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="186" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="186" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A186" s="2" t="s">
         <v>188</v>
       </c>
@@ -3948,7 +4096,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="187" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="187" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A187" s="2" t="s">
         <v>189</v>
       </c>
@@ -3962,7 +4110,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="188" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="188" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A188" s="2" t="s">
         <v>190</v>
       </c>
@@ -3976,7 +4124,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="189" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="189" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A189" s="2" t="s">
         <v>191</v>
       </c>
@@ -3990,7 +4138,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="190" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="190" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A190" s="2" t="s">
         <v>192</v>
       </c>
@@ -4004,7 +4152,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="191" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="191" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A191" s="2" t="s">
         <v>193</v>
       </c>
@@ -4018,7 +4166,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="192" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="192" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A192" s="2" t="s">
         <v>194</v>
       </c>
@@ -4032,7 +4180,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="193" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="193" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A193" s="2" t="s">
         <v>195</v>
       </c>
@@ -4046,7 +4194,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="194" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="194" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A194" s="2" t="s">
         <v>196</v>
       </c>
@@ -4060,7 +4208,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="195" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="195" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A195" s="2" t="s">
         <v>197</v>
       </c>
@@ -4074,7 +4222,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="196" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="196" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A196" s="2" t="s">
         <v>198</v>
       </c>
@@ -4088,7 +4236,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="197" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="197" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A197" s="2" t="s">
         <v>199</v>
       </c>
@@ -4102,7 +4250,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="198" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="198" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A198" s="2" t="s">
         <v>200</v>
       </c>
@@ -4116,7 +4264,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="199" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="199" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A199" s="2" t="s">
         <v>201</v>
       </c>
@@ -4130,7 +4278,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="200" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="200" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A200" s="2" t="s">
         <v>202</v>
       </c>
@@ -4144,7 +4292,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="201" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="201" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A201" s="2" t="s">
         <v>203</v>
       </c>
@@ -4158,7 +4306,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="202" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="202" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A202" s="2" t="s">
         <v>204</v>
       </c>
@@ -4172,7 +4320,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="203" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="203" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A203" s="2" t="s">
         <v>205</v>
       </c>
@@ -4186,7 +4334,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="204" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="204" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A204" s="2" t="s">
         <v>206</v>
       </c>
@@ -4200,7 +4348,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="205" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="205" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A205" s="2" t="s">
         <v>207</v>
       </c>
@@ -4214,7 +4362,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="206" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="206" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A206" s="2" t="s">
         <v>208</v>
       </c>
@@ -4228,7 +4376,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="207" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="207" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A207" s="2" t="s">
         <v>209</v>
       </c>
@@ -4242,7 +4390,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="208" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="208" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A208" s="2" t="s">
         <v>210</v>
       </c>
@@ -4256,7 +4404,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="209" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="209" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A209" s="2" t="s">
         <v>211</v>
       </c>
@@ -4270,7 +4418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="210" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="210" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A210" s="2" t="s">
         <v>212</v>
       </c>
@@ -4284,7 +4432,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="211" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="211" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A211" s="2" t="s">
         <v>213</v>
       </c>
@@ -4298,7 +4446,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="212" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="212" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A212" s="2" t="s">
         <v>214</v>
       </c>
@@ -4312,7 +4460,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="213" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="213" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A213" s="2" t="s">
         <v>215</v>
       </c>
@@ -4326,7 +4474,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="214" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="214" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A214" s="2" t="s">
         <v>216</v>
       </c>
@@ -4340,7 +4488,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="215" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="215" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A215" s="2" t="s">
         <v>217</v>
       </c>
@@ -4354,7 +4502,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="216" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="216" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A216" s="2" t="s">
         <v>218</v>
       </c>
@@ -4368,7 +4516,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="217" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="217" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A217" s="2" t="s">
         <v>219</v>
       </c>
@@ -4382,7 +4530,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="218" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="218" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A218" s="2" t="s">
         <v>220</v>
       </c>
@@ -4396,7 +4544,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="219" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="219" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A219" s="2" t="s">
         <v>221</v>
       </c>
@@ -4410,7 +4558,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="220" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="220" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A220" s="2" t="s">
         <v>222</v>
       </c>
@@ -4424,7 +4572,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="221" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="221" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A221" s="2" t="s">
         <v>223</v>
       </c>
@@ -4438,7 +4586,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="222" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="222" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A222" s="2" t="s">
         <v>224</v>
       </c>
@@ -4452,7 +4600,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="223" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="223" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A223" s="2" t="s">
         <v>225</v>
       </c>
@@ -4466,7 +4614,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="224" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="224" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A224" s="2" t="s">
         <v>226</v>
       </c>
@@ -4480,7 +4628,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="225" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="225" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A225" s="2" t="s">
         <v>227</v>
       </c>
@@ -4494,7 +4642,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="226" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="226" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A226" s="2" t="s">
         <v>228</v>
       </c>
@@ -4508,7 +4656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="227" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="227" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A227" s="2" t="s">
         <v>229</v>
       </c>
@@ -4522,7 +4670,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="228" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="228" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A228" s="2" t="s">
         <v>230</v>
       </c>
@@ -4536,7 +4684,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="229" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="229" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A229" s="2" t="s">
         <v>231</v>
       </c>
@@ -4550,7 +4698,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="230" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="230" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A230" s="2" t="s">
         <v>232</v>
       </c>
@@ -4564,7 +4712,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="231" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="231" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A231" s="2" t="s">
         <v>233</v>
       </c>
@@ -4578,7 +4726,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="232" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="232" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A232" s="2" t="s">
         <v>234</v>
       </c>
@@ -4592,7 +4740,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="233" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="233" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A233" s="2" t="s">
         <v>235</v>
       </c>
@@ -4606,7 +4754,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="234" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="234" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A234" s="2" t="s">
         <v>236</v>
       </c>
@@ -4620,7 +4768,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="235" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="235" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A235" s="2" t="s">
         <v>237</v>
       </c>
@@ -4634,7 +4782,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="236" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="236" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A236" s="2" t="s">
         <v>238</v>
       </c>
@@ -4648,7 +4796,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="237" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="237" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A237" s="2" t="s">
         <v>239</v>
       </c>
@@ -4662,7 +4810,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="238" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="238" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A238" s="2" t="s">
         <v>240</v>
       </c>
@@ -4676,7 +4824,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="239" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="239" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A239" s="2" t="s">
         <v>241</v>
       </c>
@@ -4690,7 +4838,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="240" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="240" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A240" s="2" t="s">
         <v>242</v>
       </c>
@@ -4704,7 +4852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="241" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="241" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A241" s="2" t="s">
         <v>243</v>
       </c>
@@ -4718,7 +4866,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="242" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="242" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A242" s="2" t="s">
         <v>244</v>
       </c>
@@ -4732,7 +4880,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="243" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="243" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A243" s="2" t="s">
         <v>245</v>
       </c>
@@ -4746,7 +4894,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="244" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="244" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A244" s="2" t="s">
         <v>246</v>
       </c>
@@ -4760,7 +4908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="245" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="245" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A245" s="2" t="s">
         <v>247</v>
       </c>
@@ -4774,7 +4922,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="246" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="246" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A246" s="2" t="s">
         <v>248</v>
       </c>
@@ -4788,7 +4936,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="247" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="247" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A247" s="2" t="s">
         <v>249</v>
       </c>
@@ -4802,7 +4950,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="248" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="248" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A248" s="2" t="s">
         <v>250</v>
       </c>
@@ -4816,7 +4964,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="249" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="249" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A249" s="2" t="s">
         <v>251</v>
       </c>
@@ -4830,7 +4978,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="250" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="250" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A250" s="2" t="s">
         <v>252</v>
       </c>
@@ -4844,7 +4992,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="251" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="251" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A251" s="2" t="s">
         <v>253</v>
       </c>
@@ -4858,7 +5006,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="252" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="252" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A252" s="2" t="s">
         <v>254</v>
       </c>
@@ -4872,7 +5020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="253" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="253" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A253" s="2" t="s">
         <v>255</v>
       </c>
@@ -4886,7 +5034,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="254" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="254" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A254" s="2" t="s">
         <v>256</v>
       </c>
@@ -4900,7 +5048,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="255" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="255" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A255" s="2" t="s">
         <v>257</v>
       </c>
@@ -4914,7 +5062,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="256" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="256" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A256" s="2" t="s">
         <v>258</v>
       </c>
@@ -4928,7 +5076,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="257" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="257" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A257" s="2" t="s">
         <v>259</v>
       </c>
@@ -4942,7 +5090,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="258" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="258" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A258" s="2" t="s">
         <v>260</v>
       </c>
@@ -4956,7 +5104,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="259" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="259" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A259" s="2" t="s">
         <v>261</v>
       </c>
@@ -4970,7 +5118,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="260" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="260" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A260" s="2" t="s">
         <v>262</v>
       </c>
@@ -4984,7 +5132,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="261" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="261" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A261" s="2" t="s">
         <v>263</v>
       </c>
@@ -4998,7 +5146,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="262" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="262" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A262" s="2" t="s">
         <v>264</v>
       </c>
@@ -5012,7 +5160,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="263" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="263" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A263" s="2" t="s">
         <v>265</v>
       </c>
@@ -5026,7 +5174,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="264" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="264" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A264" s="2" t="s">
         <v>266</v>
       </c>
@@ -5040,7 +5188,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="265" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="265" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A265" s="2" t="s">
         <v>267</v>
       </c>
@@ -5054,7 +5202,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="266" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="266" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A266" s="2" t="s">
         <v>268</v>
       </c>
@@ -5068,7 +5216,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="267" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="267" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A267" s="2" t="s">
         <v>269</v>
       </c>
@@ -5082,7 +5230,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="268" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="268" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A268" s="2" t="s">
         <v>270</v>
       </c>
@@ -5096,7 +5244,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="269" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="269" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A269" s="2" t="s">
         <v>271</v>
       </c>
@@ -5110,7 +5258,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="270" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="270" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A270" s="2" t="s">
         <v>272</v>
       </c>
@@ -5124,7 +5272,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="271" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="271" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A271" s="2" t="s">
         <v>273</v>
       </c>
@@ -5138,7 +5286,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="272" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="272" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A272" s="2" t="s">
         <v>274</v>
       </c>
@@ -5152,7 +5300,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="273" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="273" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A273" s="2" t="s">
         <v>275</v>
       </c>
@@ -5166,7 +5314,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="274" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="274" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A274" s="2" t="s">
         <v>276</v>
       </c>
@@ -5180,7 +5328,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="275" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="275" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A275" s="2" t="s">
         <v>277</v>
       </c>
@@ -5194,7 +5342,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="276" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="276" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A276" s="2" t="s">
         <v>278</v>
       </c>
@@ -5208,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="277" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="277" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A277" s="2" t="s">
         <v>279</v>
       </c>
@@ -5222,7 +5370,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="278" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="278" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A278" s="2" t="s">
         <v>280</v>
       </c>
@@ -5236,7 +5384,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="279" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="279" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A279" s="2" t="s">
         <v>281</v>
       </c>
@@ -5250,7 +5398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="280" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="280" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A280" s="2" t="s">
         <v>282</v>
       </c>
@@ -5264,7 +5412,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="281" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="281" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A281" s="2" t="s">
         <v>283</v>
       </c>
@@ -5278,7 +5426,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="282" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="282" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A282" s="2" t="s">
         <v>284</v>
       </c>
@@ -5292,7 +5440,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="283" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="283" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A283" s="2" t="s">
         <v>285</v>
       </c>
@@ -5306,7 +5454,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="284" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="284" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A284" s="2" t="s">
         <v>286</v>
       </c>
@@ -5320,7 +5468,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="285" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="285" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A285" s="2" t="s">
         <v>287</v>
       </c>
@@ -5334,7 +5482,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="286" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="286" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A286" s="2" t="s">
         <v>288</v>
       </c>
@@ -5348,7 +5496,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="287" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="287" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A287" s="2" t="s">
         <v>289</v>
       </c>
@@ -5362,7 +5510,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="288" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="288" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A288" s="2" t="s">
         <v>290</v>
       </c>
@@ -5376,7 +5524,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="289" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="289" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A289" s="2" t="s">
         <v>291</v>
       </c>
@@ -5390,7 +5538,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="290" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="290" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A290" s="2" t="s">
         <v>292</v>
       </c>
@@ -5404,7 +5552,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="291" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="291" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A291" s="2" t="s">
         <v>293</v>
       </c>
@@ -5418,7 +5566,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="292" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="292" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A292" s="2" t="s">
         <v>294</v>
       </c>
@@ -5432,7 +5580,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="293" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="293" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A293" s="2" t="s">
         <v>295</v>
       </c>
@@ -5446,7 +5594,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="294" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="294" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A294" s="2" t="s">
         <v>296</v>
       </c>
@@ -5460,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="295" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="295" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A295" s="2" t="s">
         <v>297</v>
       </c>
@@ -5474,7 +5622,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="296" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="296" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A296" s="2" t="s">
         <v>298</v>
       </c>
@@ -5488,7 +5636,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="297" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="297" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A297" s="2" t="s">
         <v>299</v>
       </c>
@@ -5502,7 +5650,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="298" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="298" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A298" s="2" t="s">
         <v>300</v>
       </c>
@@ -5516,7 +5664,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="299" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="299" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A299" s="2" t="s">
         <v>301</v>
       </c>
@@ -5530,7 +5678,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="300" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="300" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A300" s="2" t="s">
         <v>302</v>
       </c>
@@ -5544,7 +5692,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="301" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="301" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A301" s="2" t="s">
         <v>303</v>
       </c>
@@ -5558,7 +5706,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="302" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="302" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A302" s="2" t="s">
         <v>304</v>
       </c>
@@ -5572,7 +5720,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="303" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="303" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A303" s="2" t="s">
         <v>305</v>
       </c>
@@ -5586,7 +5734,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="304" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="304" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A304" s="2" t="s">
         <v>306</v>
       </c>
@@ -5600,7 +5748,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="305" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="305" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A305" s="2" t="s">
         <v>307</v>
       </c>
@@ -5614,7 +5762,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="306" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="306" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A306" s="2" t="s">
         <v>308</v>
       </c>
@@ -5628,7 +5776,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="307" spans="1:4" x14ac:dyDescent="0.2">
+    <row r="307" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A307" s="2" t="s">
         <v>309</v>
       </c>
@@ -5643,10 +5791,13 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:D307" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="0" priority="1"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="0.75" bottom="0.5" header="0.5" footer="0.75"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <tableParts count="1">
+    <tablePart r:id="rId2"/>
+  </tableParts>
 </worksheet>
 </file>